--- a/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
+++ b/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
@@ -569,7 +569,7 @@
     <t>DIR-01</t>
   </si>
   <si>
-    <t>Danh bạ 500+ Doanh nhân, tìm kiếm theo tên, công ty và lọc theo ngành nghề</t>
+    <t>Danh bạ Hội viên Doanh nhân, tìm kiếm theo tên, công ty và lọc theo ngành nghề</t>
   </si>
   <si>
     <t>Danh bạ phân trang mượt mà, lọc theo 12 ngành kinh tế mũi nhọn, tìm kiếm tiếng Việt không dấu siêu tốc.</t>

--- a/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
+++ b/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="445">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ PHÁT TRIỂN &amp; ĐÁNH GIÁ KỸ THUẬT ỨNG DỤNG HIỆP HỘI CEO 1983</t>
   </si>
@@ -20,10 +20,10 @@
     <t>Hệ sinh thái VIONE Connect · Đánh giá trung thực hiện trạng kiểm thử phần cứng &amp; môi trường sandbox bên thứ ba</t>
   </si>
   <si>
-    <t>63 Tính năng</t>
-  </si>
-  <si>
-    <t>59 Tính năng</t>
+    <t>70 Tính năng</t>
+  </si>
+  <si>
+    <t>66 Tính năng</t>
   </si>
   <si>
     <t>4 Tính năng</t>
@@ -152,6 +152,12 @@
     <t>Nâng Cấp Toàn Diện 14 Tính Năng &amp; Tinh Chỉnh Trải Nghiệm Doanh Nhân CEO 1983</t>
   </si>
   <si>
+    <t>MOD-13</t>
+  </si>
+  <si>
+    <t>Nâng Cấp 7 Tính Năng: HTTPS, Sự Kiện Banner Templates, Biểu Quyết, Lucky Draw, Sàn TMĐT Luxury, Bảng Tin Cơ Hội &amp; iOS PWA</t>
+  </si>
+  <si>
     <t>⚠️ LƯU Ý ĐẶC BIỆT: CÁC TÍNH NĂNG CHƯA KIỂM THỬ ĐƯỢC TRÊN MÔI TRƯỜNG DEV</t>
   </si>
   <si>
@@ -1233,6 +1239,114 @@
   </si>
   <si>
     <t>Sidebar role-based permission matrix, Pointer drag coordinates</t>
+  </si>
+  <si>
+    <t>MOD-13: NÂNG CẤP 7 TÍNH NĂNG: HTTPS, SỰ KIỆN BANNER TEMPLATES, BIỂU QUYẾT, LUCKY DRAW, SÀN TMĐT LUXURY, BẢNG TIN CƠ HỘI &amp; IOS PWA</t>
+  </si>
+  <si>
+    <t>REQ-01</t>
+  </si>
+  <si>
+    <t>Cấu hình HTTPS SSL &amp; Kịch bản Fast Deploy cho Web CRM và App Hiệp Hội</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>Sinh chứng chỉ SSL SAN hợp lệ cho IP máy chủ và tên miền sslip.io, cấu hình Nginx SSL Reverse Proxy, mở port 5443 (CRM) và 5444 (App Hiệp hội), nâng cấp script fast-deploy.ps1 hỗ trợ tham số -EnableHttps triển khai tự động.</t>
+  </si>
+  <si>
+    <t>Server Dev (14.225.217.232)</t>
+  </si>
+  <si>
+    <t>deploy/ssl/nginx.conf, deploy-ssl.ps1, fast-deploy.ps1 -EnableHttps</t>
+  </si>
+  <si>
+    <t>REQ-02</t>
+  </si>
+  <si>
+    <t>Thiết kế Banner và Bố cục Text riêng cho từng loại Sự kiện (Forum, Workshop, Networking, Training)</t>
+  </si>
+  <si>
+    <t>Xây dựng bộ template riêng cho từng loại sự kiện: Diễn đàn cấp cao (Forum), Workshop &amp; Tọa đàm, Kết nối Doanh nhân (Networking), Đào tạo &amp; Huấn luyện (Training). Khi Admin chọn loại sự kiện trên CRM, tự động điền thông tin tiêu đề, tagline, sức chứa, địa điểm và hiển thị banner preview trực tiếp.</t>
+  </si>
+  <si>
+    <t>Tạo Sự Kiện CRM (/events/new, EventWizard)</t>
+  </si>
+  <si>
+    <t>apps/vione_app_fe/src/lib/event-type-templates.ts, EventWizard.tsx</t>
+  </si>
+  <si>
+    <t>REQ-03</t>
+  </si>
+  <si>
+    <t>Thông báo Biểu Quyết Sự Kiện đẩy thời gian thực về App Hiệp Hội</t>
+  </si>
+  <si>
+    <t>Liên kết luồng biểu quyết giữa CRM và App: Khi tạo phiên biểu quyết tại CRM, hệ thống tự động phát sinh thông báo đẩy định danh về App Hiệp hội, hiển thị thẻ tương tác kèm nút "Tham gia biểu quyết ngay" đưa hội viên thẳng vào phiên bầu chọn.</t>
+  </si>
+  <si>
+    <t>Tạo Biểu Quyết CRM (/voting) &amp; Màn hình Thông báo App (/association/notifications)</t>
+  </si>
+  <si>
+    <t>POST /api/voting/sessions, connect-app.service.ts, association.notifications.tsx</t>
+  </si>
+  <si>
+    <t>REQ-04</t>
+  </si>
+  <si>
+    <t>Quay Thưởng May Mắn (Lucky Draw) từ CRM, Số Vé May Mắn Random &amp; Thông Báo Chúc Mừng</t>
+  </si>
+  <si>
+    <t>Thêm cột lucky_number và tự động sinh số may mắn ngẫu nhiên 4 chữ số (#XXXX) mỗi khi hội viên đăng ký vé sự kiện. Module LuckyDrawModal trên CRM quay số ngẫu nhiên từ danh sách vé đã đăng ký, hiển thị người trúng giải và gửi thông báo chúc mừng trúng thưởng kèm giải thưởng tức thì về App.</t>
+  </si>
+  <si>
+    <t>Quay số trúng thưởng (/voting) &amp; Thông báo App (/association/notifications)</t>
+  </si>
+  <si>
+    <t>public.event_registrations.lucky_number, POST /api/voting/lucky-draw/notify</t>
+  </si>
+  <si>
+    <t>REQ-05</t>
+  </si>
+  <si>
+    <t>Sàn Giao Thương Thương Mại Điện Tử Luxury E-Commerce với 3 Section Phân Trang</t>
+  </si>
+  <si>
+    <t>Đại tu giao diện Sàn giao thương theo phong cách E-Commerce sang trọng: Header có tìm kiếm ở giữa, menu thả xuống danh mục sản phẩm ở bên trái, icon bộ lọc và nút "Đăng SP" ở bên phải. Bố cục 3 section chuyên biệt có phân trang riêng: 1) Sản phẩm mới đăng, 2) Sản phẩm được xem nhiều nhất, 3) Doanh nghiệp/Công ty nổi bật nhất (mỗi hội viên đại diện cho 1 công ty).</t>
+  </si>
+  <si>
+    <t>GET /api/products, GET /api/marketplace/products, association.products.tsx</t>
+  </si>
+  <si>
+    <t>REQ-06</t>
+  </si>
+  <si>
+    <t>Bảng Tin Trao Cơ Hội Giao Thương: Phân Trang, Đếm Lượt Xem &amp; Danh Sách Người Quan Tâm Cho Chủ Bài</t>
+  </si>
+  <si>
+    <t>Nâng cấp giao diện Trao cơ hội dạng bảng tin có phân trang mượt mà; tích hợp bộ đếm lượt xem realtime tăng dần mỗi khi người dùng khác click xem chi tiết; riêng chủ bài đăng có thể xem danh sách đầy đủ những ai bấm quan tâm kèm nút liên hệ trực tiếp Gọi điện, Gửi email và Nhắn tin.</t>
+  </si>
+  <si>
+    <t>Màn hình Trao Cơ Hội (/association/opportunities)</t>
+  </si>
+  <si>
+    <t>GET /api/opportunities, POST /api/opportunities/:id/view, GET /api/opportunities/:id/interests</t>
+  </si>
+  <si>
+    <t>REQ-07</t>
+  </si>
+  <si>
+    <t>Cấu Hình PWA Hoàn Chỉnh Cho App Hiệp Hội (Tương Thích Mọi Thiết Bị iOS &amp; Android)</t>
+  </si>
+  <si>
+    <t>Thiết lập PWA tiêu chuẩn cho App Hiệp hội: File manifest.webmanifest với start_url: "/association", theme_color CEO 1983 (#003B95), đăng ký Service Worker sw.js hỗ trợ bộ nhớ đệm ngoại tuyến, meta tags Apple Web App Capable, và component IosInstallPrompt hiển thị hướng dẫn trực quan cài đặt "Thêm vào MH chính" trên Safari iOS.</t>
+  </si>
+  <si>
+    <t>App Hiệp Hội (/association)</t>
+  </si>
+  <si>
+    <t>public/manifest.webmanifest, public/sw.js, register-sw.ts, IosInstallPrompt.tsx</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G27"/>
+  <dimension ref="B2:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2184,29 +2298,39 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="17" t="s">
+      <c r="C22" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+      <c r="D22" s="13">
+        <v>7</v>
+      </c>
+      <c r="E22" s="13">
+        <v>7</v>
+      </c>
+      <c r="F22" s="13">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -2216,7 +2340,7 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -2224,14 +2348,24 @@
       <c r="F27" s="17"/>
       <c r="G27" s="17"/>
     </row>
+    <row r="28" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2240,7 +2374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:R79"/>
+  <dimension ref="B2:R87"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2264,7 +2398,7 @@
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -2285,60 +2419,60 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I4" s="19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M4" s="19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N4" s="19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O4" s="20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R4" s="19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -2362,52 +2496,52 @@
         <v>1</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N6" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2415,52 +2549,52 @@
         <v>2</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P7" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2468,52 +2602,52 @@
         <v>3</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="27" t="s">
         <v>28</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N8" s="27" t="s">
         <v>28</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P8" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q8" s="27" t="s">
         <v>28</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2521,52 +2655,52 @@
         <v>4</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="P9" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2574,57 +2708,57 @@
         <v>5</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P10" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -2648,52 +2782,52 @@
         <v>6</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K12" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N12" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2701,52 +2835,52 @@
         <v>7</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="K13" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="23" t="s">
-        <v>109</v>
-      </c>
       <c r="P13" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q13" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2754,52 +2888,52 @@
         <v>8</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K14" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N14" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P14" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2807,52 +2941,52 @@
         <v>9</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K15" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M15" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N15" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P15" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q15" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R15" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2860,57 +2994,57 @@
         <v>10</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K16" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M16" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N16" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O16" s="23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P16" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R16" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -2934,52 +3068,52 @@
         <v>11</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K18" s="27" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="M18" s="26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N18" s="27" t="s">
         <v>25</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="P18" s="26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q18" s="27" t="s">
         <v>25</v>
       </c>
       <c r="R18" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2987,57 +3121,57 @@
         <v>12</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K19" s="27" t="s">
         <v>25</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M19" s="26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N19" s="27" t="s">
         <v>25</v>
       </c>
       <c r="O19" s="23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P19" s="26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q19" s="27" t="s">
         <v>25</v>
       </c>
       <c r="R19" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
@@ -3061,52 +3195,52 @@
         <v>13</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J21" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M21" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O21" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P21" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R21" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3114,52 +3248,52 @@
         <v>14</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K22" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M22" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N22" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O22" s="23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P22" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q22" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3167,52 +3301,52 @@
         <v>15</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K23" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M23" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N23" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O23" s="23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P23" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q23" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3220,52 +3354,52 @@
         <v>16</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K24" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N24" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O24" s="23" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P24" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q24" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R24" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3273,52 +3407,52 @@
         <v>17</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K25" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M25" s="26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N25" s="27" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O25" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="P25" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q25" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="P25" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q25" s="27" t="s">
-        <v>169</v>
-      </c>
       <c r="R25" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3326,52 +3460,52 @@
         <v>18</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K26" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M26" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N26" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O26" s="23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P26" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q26" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3379,57 +3513,57 @@
         <v>19</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K27" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M27" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N27" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O27" s="23" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P27" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q27" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R27" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -3453,52 +3587,52 @@
         <v>20</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K29" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M29" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N29" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O29" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P29" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3506,52 +3640,52 @@
         <v>21</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K30" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M30" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N30" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O30" s="23" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P30" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q30" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3559,52 +3693,52 @@
         <v>22</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>30</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K31" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M31" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N31" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O31" s="23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P31" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q31" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3612,57 +3746,57 @@
         <v>23</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K32" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M32" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N32" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O32" s="23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P32" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q32" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R32" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -3686,52 +3820,52 @@
         <v>24</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>32</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K34" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M34" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N34" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O34" s="23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P34" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q34" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3739,52 +3873,52 @@
         <v>25</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>32</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K35" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M35" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N35" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O35" s="23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q35" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3792,57 +3926,57 @@
         <v>26</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>32</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J36" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K36" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M36" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N36" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O36" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P36" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="21" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
@@ -3866,52 +4000,52 @@
         <v>27</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>34</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K38" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M38" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N38" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O38" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P38" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q38" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3919,52 +4053,52 @@
         <v>28</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>34</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J39" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K39" s="27" t="s">
         <v>28</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N39" s="27" t="s">
         <v>28</v>
       </c>
       <c r="O39" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P39" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="27" t="s">
         <v>28</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3972,57 +4106,57 @@
         <v>29</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>34</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K40" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M40" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N40" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O40" s="23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P40" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q40" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B41" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -4046,52 +4180,52 @@
         <v>30</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>36</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K42" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M42" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N42" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O42" s="23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P42" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q42" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4099,52 +4233,52 @@
         <v>31</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>36</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J43" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K43" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M43" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N43" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P43" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q43" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4152,57 +4286,57 @@
         <v>32</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>36</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K44" s="27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N44" s="27" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O44" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="P44" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q44" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="P44" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q44" s="27" t="s">
-        <v>251</v>
-      </c>
       <c r="R44" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -4226,52 +4360,52 @@
         <v>33</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>39</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K46" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M46" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N46" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O46" s="23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P46" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q46" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R46" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4279,52 +4413,52 @@
         <v>34</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>39</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K47" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M47" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N47" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O47" s="23" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P47" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q47" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R47" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4332,52 +4466,52 @@
         <v>35</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>39</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K48" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M48" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N48" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O48" s="23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P48" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q48" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R48" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4385,52 +4519,52 @@
         <v>36</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>39</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I49" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J49" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K49" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N49" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O49" s="23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P49" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4438,57 +4572,57 @@
         <v>37</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>39</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J50" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K50" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N50" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O50" s="23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P50" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q50" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B51" s="21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
@@ -4512,52 +4646,52 @@
         <v>38</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>41</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K52" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N52" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O52" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P52" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q52" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R52" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4565,57 +4699,57 @@
         <v>39</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>41</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K53" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L53" s="23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M53" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N53" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O53" s="23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P53" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q53" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R53" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B54" s="21" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
@@ -4639,52 +4773,52 @@
         <v>40</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J55" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K55" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N55" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O55" s="23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P55" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q55" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R55" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4692,52 +4826,52 @@
         <v>41</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K56" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N56" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O56" s="23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P56" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q56" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R56" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4745,52 +4879,52 @@
         <v>42</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K57" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N57" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O57" s="23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="P57" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q57" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4798,52 +4932,52 @@
         <v>43</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K58" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L58" s="23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N58" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O58" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P58" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q58" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R58" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4851,52 +4985,52 @@
         <v>44</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K59" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L59" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N59" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O59" s="23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P59" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q59" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R59" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4904,52 +5038,52 @@
         <v>45</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K60" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M60" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N60" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O60" s="23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P60" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q60" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R60" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -4957,52 +5091,52 @@
         <v>46</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K61" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L61" s="23" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M61" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N61" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O61" s="23" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P61" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q61" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5010,57 +5144,57 @@
         <v>47</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>43</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K62" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M62" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N62" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O62" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P62" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q62" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B63" s="21" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
@@ -5084,52 +5218,52 @@
         <v>48</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K64" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M64" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N64" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O64" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P64" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q64" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R64" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5137,52 +5271,52 @@
         <v>49</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G65" s="23" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J65" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K65" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M65" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N65" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O65" s="23" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P65" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q65" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R65" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5190,52 +5324,52 @@
         <v>50</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J66" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K66" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L66" s="23" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M66" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N66" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O66" s="23" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P66" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q66" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R66" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5243,52 +5377,52 @@
         <v>51</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D67" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J67" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K67" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M67" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N67" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O67" s="23" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P67" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q67" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R67" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5296,52 +5430,52 @@
         <v>52</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D68" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G68" s="23" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J68" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K68" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L68" s="23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N68" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O68" s="23" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P68" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q68" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R68" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5349,52 +5483,52 @@
         <v>53</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J69" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K69" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M69" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N69" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O69" s="23" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P69" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q69" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R69" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5402,52 +5536,52 @@
         <v>54</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D70" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K70" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M70" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N70" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O70" s="23" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P70" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q70" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R70" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5455,52 +5589,52 @@
         <v>55</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D71" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J71" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K71" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L71" s="23" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M71" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N71" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O71" s="23" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P71" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q71" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R71" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5508,52 +5642,52 @@
         <v>56</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D72" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G72" s="23" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J72" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K72" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N72" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O72" s="23" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P72" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q72" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R72" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5561,52 +5695,52 @@
         <v>57</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D73" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K73" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="M73" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N73" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O73" s="23" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q73" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R73" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5614,52 +5748,52 @@
         <v>58</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D74" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K74" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M74" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N74" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O74" s="23" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P74" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q74" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R74" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5667,52 +5801,52 @@
         <v>59</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D75" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G75" s="23" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J75" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K75" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L75" s="23" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M75" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N75" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O75" s="23" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P75" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q75" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5720,52 +5854,52 @@
         <v>60</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D76" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G76" s="23" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K76" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M76" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N76" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O76" s="23" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P76" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q76" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5773,52 +5907,52 @@
         <v>61</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D77" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G77" s="23" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K77" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L77" s="23" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M77" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N77" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O77" s="23" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P77" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q77" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R77" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5826,52 +5960,52 @@
         <v>62</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D78" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G78" s="23" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K78" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L78" s="23" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N78" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O78" s="23" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P78" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q78" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R78" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -5879,56 +6013,448 @@
         <v>63</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D79" s="23" t="s">
         <v>45</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G79" s="23" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J79" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K79" s="25" t="s">
         <v>22</v>
       </c>
       <c r="L79" s="23" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M79" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N79" s="25" t="s">
         <v>22</v>
       </c>
       <c r="O79" s="23" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P79" s="25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q79" s="25" t="s">
         <v>22</v>
       </c>
       <c r="R79" s="23" t="s">
-        <v>79</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B80" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="21"/>
+      <c r="K80" s="21"/>
+      <c r="L80" s="21"/>
+      <c r="M80" s="21"/>
+      <c r="N80" s="21"/>
+      <c r="O80" s="21"/>
+      <c r="P80" s="21"/>
+      <c r="Q80" s="21"/>
+      <c r="R80" s="21"/>
+    </row>
+    <row r="81" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B81" s="22">
+        <v>64</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="F81" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G81" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="H81" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I81" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J81" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K81" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="M81" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N81" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O81" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="P81" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q81" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R81" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B82" s="22">
+        <v>65</v>
+      </c>
+      <c r="C82" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="F82" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G82" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I82" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J82" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K82" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="M82" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N82" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O82" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="P82" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q82" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R82" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B83" s="22">
+        <v>66</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="F83" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G83" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="H83" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I83" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J83" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K83" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L83" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="M83" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N83" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O83" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="P83" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R83" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B84" s="22">
+        <v>67</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="D84" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="F84" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G84" s="23" t="s">
+        <v>428</v>
+      </c>
+      <c r="H84" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I84" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J84" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K84" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L84" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="M84" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N84" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" s="23" t="s">
+        <v>430</v>
+      </c>
+      <c r="P84" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q84" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R84" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B85" s="22">
+        <v>68</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="F85" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G85" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="H85" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I85" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J85" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K85" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L85" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M85" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N85" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O85" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="P85" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R85" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B86" s="22">
+        <v>69</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E86" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="F86" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G86" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="H86" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I86" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J86" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K86" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L86" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="M86" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N86" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O86" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="P86" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q86" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R86" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B87" s="22">
+        <v>70</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>441</v>
+      </c>
+      <c r="F87" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="G87" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="H87" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I87" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J87" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K87" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L87" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="M87" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="N87" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="O87" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="P87" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q87" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="R87" s="23" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B5:R5"/>
     <mergeCell ref="B11:R11"/>
@@ -5942,6 +6468,7 @@
     <mergeCell ref="B51:R51"/>
     <mergeCell ref="B54:R54"/>
     <mergeCell ref="B63:R63"/>
+    <mergeCell ref="B80:R80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
+++ b/document/TIEN_DO_CONG_VIEC_APP_HIEP_HOI_CHI_TIET.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="509">
   <si>
     <t>BÁO CÁO TIẾN ĐỘ PHÁT TRIỂN &amp; ĐÁNH GIÁ KỸ THUẬT ỨNG DỤNG HIỆP HỘI CEO 1983</t>
   </si>
@@ -20,16 +20,16 @@
     <t>Hệ sinh thái VIONE Connect · Đánh giá trung thực hiện trạng kiểm thử phần cứng &amp; môi trường sandbox bên thứ ba</t>
   </si>
   <si>
-    <t>70 Tính năng</t>
-  </si>
-  <si>
-    <t>66 Tính năng</t>
+    <t>84 Tính năng</t>
+  </si>
+  <si>
+    <t>80 Tính năng</t>
   </si>
   <si>
     <t>4 Tính năng</t>
   </si>
   <si>
-    <t>98%</t>
+    <t>99%</t>
   </si>
   <si>
     <t>TỔNG TÍNH NĂNG CON</t>
@@ -71,9 +71,6 @@
     <t>Xác Thực, Đăng Nhập &amp; Kích Hoạt Thẻ Hội Viên</t>
   </si>
   <si>
-    <t>99%</t>
-  </si>
-  <si>
     <t>MOD-02</t>
   </si>
   <si>
@@ -638,49 +635,148 @@
     <t>B2B-01</t>
   </si>
   <si>
-    <t>Sàn đăng tin Cơ hội Giao thương B2B (Chào mua, Chào bán, Đầu tư)</t>
-  </si>
-  <si>
-    <t>Phân hệ sàn giao thương B2B nội khối, gắn thẻ Chào Mua/Chào Bán/Hợp Tác, định giá hợp đồng dự kiến.</t>
+    <t>Sàn B2B Marketplace phong cách E-Commerce Luxury</t>
+  </si>
+  <si>
+    <t>Phân hệ sàn giao thương B2B nội khối, thiết kế lưới sản phẩm luxury với nhãn giá ưu đãi hội viên và bộ nhận diện thương hiệu.</t>
+  </si>
+  <si>
+    <t>Màn hình Sản phẩm (/association/products)</t>
+  </si>
+  <si>
+    <t>GET /api/connect-app/products, GET /api/marketplace/products</t>
+  </si>
+  <si>
+    <t>B2B-02</t>
+  </si>
+  <si>
+    <t>Header tìm kiếm thông minh &amp; Dropdown danh mục ngành hàng</t>
+  </si>
+  <si>
+    <t>Header có thanh tìm kiếm ở giữa, menu thả xuống danh mục sản phẩm mũi nhọn ở bên trái và bộ lọc sắp xếp.</t>
+  </si>
+  <si>
+    <t>GET /api/categories, Fuse.js Search Engine</t>
+  </si>
+  <si>
+    <t>B2B-03</t>
+  </si>
+  <si>
+    <t>Bố cục 3 Section phân trang độc lập (Mới đăng, Xem nhiều, Doanh nghiệp nổi bật)</t>
+  </si>
+  <si>
+    <t>Bố cục 3 section chuyên biệt có phân trang riêng: 1) Sản phẩm mới đăng, 2) Sản phẩm xem nhiều nhất, 3) Doanh nghiệp nổi bật nhất.</t>
+  </si>
+  <si>
+    <t>association.products.tsx Section Controllers</t>
+  </si>
+  <si>
+    <t>B2B-04</t>
+  </si>
+  <si>
+    <t>Modal Đăng sản phẩm 2 phần với tải ảnh độ nét cao</t>
+  </si>
+  <si>
+    <t>Form 2 phần thu thập thông tin cơ bản và thông tin thương mại, tích hợp upload ảnh MinIO S3 dung lượng cao.</t>
+  </si>
+  <si>
+    <t>Modal Đăng Sản Phẩm (/association/products)</t>
+  </si>
+  <si>
+    <t>POST /api/connect-app/products, POST /api/upload/file</t>
+  </si>
+  <si>
+    <t>B2B-05</t>
+  </si>
+  <si>
+    <t>Modal Chi tiết sản phẩm &amp; Định dạng giá tiền VND thông minh</t>
+  </si>
+  <si>
+    <t>Xem chi tiết sản phẩm, zoom ảnh carousel, định dạng giá tiền chuẩn VND và hiển thị hồ sơ công ty chủ quản.</t>
+  </si>
+  <si>
+    <t>Modal Chi Tiết SP (/association/products)</t>
+  </si>
+  <si>
+    <t>GET /api/products/:id, Intl.NumberFormat</t>
+  </si>
+  <si>
+    <t>B2B-06</t>
+  </si>
+  <si>
+    <t>Menu 3 chấm chỉnh sửa và xóa bài đăng sản phẩm</t>
+  </si>
+  <si>
+    <t>Menu 3 chấm tác vụ bài viết cho phép chủ sở hữu sửa thông tin hoặc xóa bài niêm yết khỏi sàn.</t>
+  </si>
+  <si>
+    <t>Thẻ Sản phẩm (/association/products)</t>
+  </si>
+  <si>
+    <t>PUT /api/connect-app/products/:id, DELETE /api/connect-app/products/:id</t>
+  </si>
+  <si>
+    <t>B2B-07</t>
+  </si>
+  <si>
+    <t>Đồng bộ &amp; Kiểm duyệt sản phẩm trên Web CRM</t>
+  </si>
+  <si>
+    <t>Ban Thư Ký kiểm duyệt sản phẩm từ App đẩy lên, gắn nhãn Hot / Ưu đãi và ẩn sản phẩm vi phạm.</t>
+  </si>
+  <si>
+    <t>CRM Sàn Giao Thương (/marketplace)</t>
+  </si>
+  <si>
+    <t>GET/PUT /api/crm/marketplace/products</t>
+  </si>
+  <si>
+    <t>B2B-08</t>
+  </si>
+  <si>
+    <t>Bảng tin Cơ hội B2B Social Feed với bộ đếm lượt xem realtime</t>
+  </si>
+  <si>
+    <t>Bảng tin trao đổi cơ hội mua bán/đầu tư theo phong cách mạng xã hội doanh nhân, tự động tăng view khi mở xem.</t>
   </si>
   <si>
     <t>Màn hình Cơ hội B2B (/association/opportunities)</t>
   </si>
   <si>
-    <t>GET /api/connect-app/opportunities, POST /api/connect-app/opportunities</t>
-  </si>
-  <si>
-    <t>B2B-02</t>
-  </si>
-  <si>
-    <t>Popup Đăng tin giao thương &amp; Đính kèm hồ sơ năng lực / hình ảnh</t>
-  </si>
-  <si>
-    <t>Form đăng tin đa phương tiện, tải ảnh lên MinIO S3 và cơ chế kiểm duyệt nội dung an toàn.</t>
-  </si>
-  <si>
-    <t>Popup Tạo bài viết B2B (/association/opportunities)</t>
+    <t>GET /api/opportunities, POST /api/opportunities/:id/view</t>
+  </si>
+  <si>
+    <t>B2B-09</t>
+  </si>
+  <si>
+    <t>Modal Đăng tin Cơ hội giao thương &amp; Đính kèm hồ sơ năng lực</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>Modal soạn thảo tin đăng cơ hội giao thương, đính kèm profile công ty và hình ảnh sản phẩm mẫu.</t>
+  </si>
+  <si>
+    <t>Modal Tạo Cơ Hội (/association/opportunities)</t>
   </si>
   <si>
     <t>POST /api/connect-app/opportunities, POST /api/upload/file</t>
   </si>
   <si>
-    <t>B2B-03</t>
-  </si>
-  <si>
-    <t>Gian hàng sản phẩm &amp; Bố cục nút "Đăng sản phẩm" tối ưu</t>
-  </si>
-  <si>
-    <t>15/09/2026 - 16/09/2026</t>
-  </si>
-  <si>
-    <t>Tái thiết kế giao diện: Chuyển nút "Đăng sản phẩm" xuống cạnh thanh tìm kiếm, nâng cấp thẻ sản phẩm với ảnh lớn sắc nét, huy hiệu chiết khấu nội bộ và nút nhận báo giá nhanh.</t>
-  </si>
-  <si>
-    <t>Màn hình Sản phẩm (/association/products)</t>
-  </si>
-  <si>
-    <t>GET /api/connect-app/products, POST /api/connect-app/products</t>
+    <t>B2B-10</t>
+  </si>
+  <si>
+    <t>Modal Danh sách thành viên Quan tâm cơ hội kèm nút Gọi/Email/Chat</t>
+  </si>
+  <si>
+    <t>Chủ bài đăng xem danh sách các CEO bấm quan tâm cơ hội, hỗ trợ kết nối nhanh qua Gọi, Email và Chat.</t>
+  </si>
+  <si>
+    <t>Modal Đối tác quan tâm (/association/opportunities)</t>
+  </si>
+  <si>
+    <t>GET /api/opportunities/:id/interests</t>
   </si>
   <si>
     <t>MOD-07: SỰ KIỆN TRÀN VIỀN, CHECK-IN QR &amp; BIỂU QUYẾT BẦU CỬ</t>
@@ -689,46 +785,151 @@
     <t>EVT-01</t>
   </si>
   <si>
-    <t>Giao diện Sự kiện Full-Image chuẩn điện ảnh (Text nằm trọn trong ảnh)</t>
-  </si>
-  <si>
-    <t>Đại tu UI Sự kiện: Toàn bộ tiêu đề, thời gian, tên sự kiện được đưa vào bên trong banner tỷ lệ 16:9 với lớp phủ gradient tối sang trọng, gắn liền dải thông số 3 cột (Thời gian, Địa điểm, Đối tượng), loại bỏ nút bấm thừa dưới chân thẻ.</t>
-  </si>
-  <si>
-    <t>Màn hình Sự kiện (/association/events &amp; /association/index)</t>
-  </si>
-  <si>
-    <t>GET /api/events, POST /api/events/:id/register</t>
+    <t>CRM Modal Tạo sự kiện với mẫu Template theo loại hình (Forum, Workshop, Networking, Training)</t>
+  </si>
+  <si>
+    <t>Tự động điền tiêu đề, địa điểm chuẩn, sức chứa và hiển thị khung xem trước Banner preview theo từng loại hình sự kiện.</t>
+  </si>
+  <si>
+    <t>Tạo Sự Kiện CRM (/events/new, EventWizard)</t>
+  </si>
+  <si>
+    <t>apps/vione_app_fe/src/lib/event-type-templates.ts, EventWizard.tsx</t>
   </si>
   <si>
     <t>EVT-02</t>
   </si>
   <si>
-    <t>Check-in bằng mã QR tại cửa hội trường &amp; Quét mã điểm danh</t>
-  </si>
-  <si>
-    <t>Sinh vé điện tử có QR định danh vé mời, quét camera check-in tự động xác nhận tham dự sự kiện.</t>
-  </si>
-  <si>
-    <t>Popup QR Check-in (/association/card, /history)</t>
-  </si>
-  <si>
-    <t>POST /api/events/:id/checkin, GET /api/events/:id/attendees</t>
+    <t>CRM Cấu hình Giá vé: Case 1 Miễn phí (0đ) &amp; Case 2 Thu phí (500.000 VNĐ)</t>
+  </si>
+  <si>
+    <t>Thiết lập 2 luồng sự kiện rõ ràng: Vé Miễn phí 0đ dành cho hội viên hoặc Vé Thu phí 500k cho Gala Dinner.</t>
+  </si>
+  <si>
+    <t>Modal Tạo Sự Kiện CRM (/events)</t>
+  </si>
+  <si>
+    <t>POST /api/events, event.ticketPrice configuration</t>
   </si>
   <si>
     <t>EVT-03</t>
   </si>
   <si>
-    <t>Biểu quyết &amp; Bầu cử trực tiếp đại hội (Thời gian thực)</t>
-  </si>
-  <si>
-    <t>Module bỏ phiếu đại biểu kín, mã hóa kết quả, bảng điều khiển kết quả biểu quyết thời gian thực.</t>
-  </si>
-  <si>
-    <t>Màn hình Biểu quyết (/association/voting)</t>
-  </si>
-  <si>
-    <t>GET /api/voting/sessions, POST /api/voting/:id/vote, GET /api/voting/:id/results</t>
+    <t>CRM Sơ đồ Khán phòng Cinema Hall Seating Map kéo thả ghế ngồi</t>
+  </si>
+  <si>
+    <t>Công cụ kéo thả định vị sơ đồ ghế ngồi trực quan, phân khu hàng ghế VIP Lãnh đạo, Thương gia và Tiêu chuẩn.</t>
+  </si>
+  <si>
+    <t>Sơ đồ Khán phòng CRM (/events/seating)</t>
+  </si>
+  <si>
+    <t>CinemaSeatingMap.tsx, Pointer drag coordinates</t>
+  </si>
+  <si>
+    <t>EVT-04</t>
+  </si>
+  <si>
+    <t>CRM Quản lý Danh sách Đại biểu &amp; Máy quét mã QR Điểm danh tốc độ cao</t>
+  </si>
+  <si>
+    <t>Quét camera mã QR trên vé Pass của đại biểu tại cổng hội trường, âm thanh bíp xác nhận và đổi trạng thái điểm danh trong 1s.</t>
+  </si>
+  <si>
+    <t>Điểm danh CRM (/events/checkin, /events/:id/attendees)</t>
+  </si>
+  <si>
+    <t>POST /api/events/:id/checkin, HTML5 QR Scanner</t>
+  </si>
+  <si>
+    <t>EVT-05</t>
+  </si>
+  <si>
+    <t>App Màn hình Danh sách Sự kiện tràn viền hiển thị thẻ Miễn phí 0đ và Có phí</t>
+  </si>
+  <si>
+    <t>Giao diện poster dọc 2:3 phong cách điện ảnh với hiệu ứng sóng ánh sáng động Golden Swoosh Wave và nhãn tag giá rõ ràng.</t>
+  </si>
+  <si>
+    <t>Màn hình Sự kiện (/association/events)</t>
+  </si>
+  <si>
+    <t>GET /api/events, association.events.tsx</t>
+  </si>
+  <si>
+    <t>EVT-06</t>
+  </si>
+  <si>
+    <t>App Modal Chi tiết Sự kiện Miễn phí &amp; Nhận vé Pass tức thì kèm Lucky #XXXX</t>
+  </si>
+  <si>
+    <t>Luồng Case 1: Đăng ký vé 0đ xác nhận tức thì, sinh mã định danh REG-XXXX và cấp mã số may mắn #XXXX quay thưởng.</t>
+  </si>
+  <si>
+    <t>Modal Đăng ký Sự Kiện (/association/events)</t>
+  </si>
+  <si>
+    <t>POST /api/events/:id/register, lucky_number generator</t>
+  </si>
+  <si>
+    <t>EVT-07</t>
+  </si>
+  <si>
+    <t>App Modal Chi tiết Sự kiện Thu phí &amp; Cổng thanh toán VietQR Napas 247</t>
+  </si>
+  <si>
+    <t>Luồng Case 2: Đăng ký vé 500k hiển thị bảng tóm tắt chi phí, chọn số lượng vé và sinh mã VietQR Napas 247 động.</t>
+  </si>
+  <si>
+    <t>Modal Thanh Toán Sự Kiện (/association/events)</t>
+  </si>
+  <si>
+    <t>POST /api/events/:id/register, VietQR Generator</t>
+  </si>
+  <si>
+    <t>EVT-08</t>
+  </si>
+  <si>
+    <t>App Màn hình Quản lý Thẻ vé Check-in của tôi với mã QR động</t>
+  </si>
+  <si>
+    <t>Ví lưu trữ toàn bộ vé sự kiện của hội viên với mã QR động sẵn sàng quét điểm danh tại bàn lễ tân.</t>
+  </si>
+  <si>
+    <t>Màn hình Check-in (/association/checkin)</t>
+  </si>
+  <si>
+    <t>GET /api/members/me/tickets, QRCode Canvas</t>
+  </si>
+  <si>
+    <t>EVT-09</t>
+  </si>
+  <si>
+    <t>App &amp; CRM Hệ thống Biểu quyết Trực tiếp (Live Voting) thời gian thực</t>
+  </si>
+  <si>
+    <t>CRM kích hoạt phiên bầu cử, App nhận thông báo đẩy tức thì mở popup biểu quyết, tổng hợp kết quả biểu đồ lên màn LED.</t>
+  </si>
+  <si>
+    <t>CRM (/voting) &amp; App (/association/voting, /notifications)</t>
+  </si>
+  <si>
+    <t>POST /api/voting/sessions, Socket.io voting:started</t>
+  </si>
+  <si>
+    <t>EVT-10</t>
+  </si>
+  <si>
+    <t>App &amp; CRM Vòng quay May mắn (Lucky Draw) &amp; Thẻ thông báo chúc mừng mạ vàng VIP</t>
+  </si>
+  <si>
+    <t>CRM quay số ngẫu nhiên theo mã số #XXXX, gửi thông báo chúc mừng trúng giải kèm thẻ vàng cúp vinh danh về App hội viên.</t>
+  </si>
+  <si>
+    <t>CRM (/voting) &amp; App (/association/notifications)</t>
+  </si>
+  <si>
+    <t>POST /api/voting/lucky-draw/notify, event_registrations.lucky_number</t>
   </si>
   <si>
     <t>MOD-08: THU &amp; ĐÓNG HỘI PHÍ TỰ ĐỘNG QUA VIETQR NAPAS 247</t>
@@ -1109,9 +1310,6 @@
     <t>GET /marketplace/products, LocalStorage vba_interested_products_${userId}</t>
   </si>
   <si>
-    <t>EVT-04</t>
-  </si>
-  <si>
     <t>Thẻ sự kiện Poster 2:3 có nhãn độ tuổi (16+, 18+, 13+) &amp; Backdrop sân khấu /events</t>
   </si>
   <si>
@@ -1269,12 +1467,6 @@
   </si>
   <si>
     <t>Xây dựng bộ template riêng cho từng loại sự kiện: Diễn đàn cấp cao (Forum), Workshop &amp; Tọa đàm, Kết nối Doanh nhân (Networking), Đào tạo &amp; Huấn luyện (Training). Khi Admin chọn loại sự kiện trên CRM, tự động điền thông tin tiêu đề, tagline, sức chứa, địa điểm và hiển thị banner preview trực tiếp.</t>
-  </si>
-  <si>
-    <t>Tạo Sự Kiện CRM (/events/new, EventWizard)</t>
-  </si>
-  <si>
-    <t>apps/vione_app_fe/src/lib/event-type-templates.ts, EventWizard.tsx</t>
   </si>
   <si>
     <t>REQ-03</t>
@@ -2075,15 +2267,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>20</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="D11" s="13">
         <v>5</v>
@@ -2095,15 +2287,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>23</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="D12" s="13">
         <v>2</v>
@@ -2115,15 +2307,15 @@
         <v>2</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>27</v>
       </c>
       <c r="D13" s="13">
         <v>7</v>
@@ -2135,15 +2327,15 @@
         <v>1</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>30</v>
       </c>
       <c r="D14" s="13">
         <v>4</v>
@@ -2155,55 +2347,55 @@
         <v>0</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="D15" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E15" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" s="13">
         <v>0</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="D16" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E16" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F16" s="13">
         <v>0</v>
       </c>
-      <c r="G16" s="14" t="s">
-        <v>5</v>
+      <c r="G16" s="15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>35</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>36</v>
       </c>
       <c r="D17" s="13">
         <v>3</v>
@@ -2215,15 +2407,15 @@
         <v>1</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>39</v>
       </c>
       <c r="D18" s="13">
         <v>5</v>
@@ -2235,15 +2427,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>40</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>41</v>
       </c>
       <c r="D19" s="13">
         <v>2</v>
@@ -2255,15 +2447,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="D20" s="13">
         <v>8</v>
@@ -2275,15 +2467,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>45</v>
       </c>
       <c r="D21" s="13">
         <v>16</v>
@@ -2295,15 +2487,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="D22" s="13">
         <v>7</v>
@@ -2315,12 +2507,12 @@
         <v>0</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -2330,7 +2522,7 @@
     </row>
     <row r="26" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -2340,7 +2532,7 @@
     </row>
     <row r="27" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -2350,7 +2542,7 @@
     </row>
     <row r="28" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -2374,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:R87"/>
+  <dimension ref="B2:R101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2398,7 +2590,7 @@
   <sheetData>
     <row r="2" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B2" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -2419,60 +2611,60 @@
     </row>
     <row r="4" ht="32" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="G4" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="I4" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="J4" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="K4" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="L4" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="M4" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="N4" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="O4" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="P4" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="Q4" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="R4" s="19" t="s">
         <v>68</v>
-      </c>
-      <c r="R4" s="19" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -2496,52 +2688,52 @@
         <v>1</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="G6" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>74</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="23" t="s">
+      <c r="M6" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N6" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>79</v>
-      </c>
       <c r="P6" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R6" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2549,52 +2741,52 @@
         <v>2</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="23" t="s">
+      <c r="M7" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N7" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>87</v>
-      </c>
       <c r="P7" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R7" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2602,52 +2794,52 @@
         <v>3</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="G8" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="H8" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="26" t="s">
+      <c r="J8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="J8" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K8" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="23" t="s">
+      <c r="M8" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="M8" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N8" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>94</v>
-      </c>
       <c r="P8" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R8" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2655,52 +2847,52 @@
         <v>4</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="F9" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" s="23" t="s">
+      <c r="H9" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="23" t="s">
+      <c r="M9" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="M9" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N9" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>99</v>
-      </c>
       <c r="P9" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R9" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2708,57 +2900,57 @@
         <v>5</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="G10" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="H10" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="23" t="s">
+      <c r="M10" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="M10" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N10" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O10" s="23" t="s">
-        <v>105</v>
-      </c>
       <c r="P10" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R10" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
@@ -2782,52 +2974,52 @@
         <v>6</v>
       </c>
       <c r="C12" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="23" t="s">
+      <c r="F12" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="23" t="s">
+      <c r="H12" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K12" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="23" t="s">
+      <c r="M12" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N12" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="M12" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N12" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O12" s="23" t="s">
-        <v>111</v>
-      </c>
       <c r="P12" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q12" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R12" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2835,52 +3027,52 @@
         <v>7</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="23" t="s">
+      <c r="F13" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="G13" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>115</v>
-      </c>
       <c r="H13" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="M13" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="M13" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N13" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="23" t="s">
-        <v>111</v>
-      </c>
       <c r="P13" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R13" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2888,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="C14" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="23" t="s">
+      <c r="F14" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G14" s="23" t="s">
+      <c r="H14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N14" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K14" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="M14" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N14" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>119</v>
-      </c>
       <c r="P14" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q14" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R14" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2941,52 +3133,52 @@
         <v>9</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="23" t="s">
+      <c r="F15" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G15" s="23" t="s">
+      <c r="H15" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="23" t="s">
+      <c r="M15" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="M15" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>124</v>
-      </c>
       <c r="P15" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q15" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R15" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -2994,57 +3186,57 @@
         <v>10</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="23" t="s">
+      <c r="F16" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G16" s="23" t="s">
+      <c r="H16" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="23" t="s">
+      <c r="M16" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="M16" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O16" s="23" t="s">
-        <v>129</v>
-      </c>
       <c r="P16" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R16" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21"/>
@@ -3068,52 +3260,52 @@
         <v>11</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="F18" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18" s="26" t="s">
+      <c r="L18" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="K18" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="23" t="s">
+      <c r="M18" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="M18" s="26" t="s">
+      <c r="N18" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O18" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="N18" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="O18" s="23" t="s">
+      <c r="P18" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="P18" s="26" t="s">
-        <v>139</v>
-      </c>
       <c r="Q18" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R18" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3121,57 +3313,57 @@
         <v>12</v>
       </c>
       <c r="C19" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="F19" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="K19" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="23" t="s">
+      <c r="L19" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="23" t="s">
+      <c r="M19" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="M19" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="N19" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>144</v>
-      </c>
       <c r="P19" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q19" s="27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R19" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
@@ -3195,52 +3387,52 @@
         <v>13</v>
       </c>
       <c r="C21" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="23" t="s">
+      <c r="F21" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="G21" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="H21" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="23" t="s">
+      <c r="M21" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N21" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="M21" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N21" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O21" s="23" t="s">
-        <v>151</v>
-      </c>
       <c r="P21" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R21" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3248,52 +3440,52 @@
         <v>14</v>
       </c>
       <c r="C22" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="D22" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="23" t="s">
+      <c r="F22" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="23" t="s">
+      <c r="H22" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L22" s="23" t="s">
+      <c r="M22" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="M22" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N22" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>156</v>
-      </c>
       <c r="P22" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q22" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R22" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3301,52 +3493,52 @@
         <v>15</v>
       </c>
       <c r="C23" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="23" t="s">
+      <c r="F23" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" s="23" t="s">
+      <c r="H23" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" s="23" t="s">
+      <c r="M23" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N23" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="M23" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N23" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O23" s="23" t="s">
-        <v>161</v>
-      </c>
       <c r="P23" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q23" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R23" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3354,52 +3546,52 @@
         <v>16</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="D24" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="23" t="s">
+      <c r="F24" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="F24" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="23" t="s">
+      <c r="H24" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I24" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K24" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L24" s="23" t="s">
+      <c r="M24" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N24" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="M24" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O24" s="23" t="s">
-        <v>166</v>
-      </c>
       <c r="P24" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R24" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3407,52 +3599,52 @@
         <v>17</v>
       </c>
       <c r="C25" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="23" t="s">
+      <c r="F25" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="G25" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="H25" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="K25" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="H25" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="J25" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="K25" s="27" t="s">
+      <c r="L25" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="L25" s="23" t="s">
+      <c r="M25" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="N25" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="O25" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="M25" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="N25" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="O25" s="23" t="s">
-        <v>173</v>
-      </c>
       <c r="P25" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q25" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R25" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3460,52 +3652,52 @@
         <v>18</v>
       </c>
       <c r="C26" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="D26" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="23" t="s">
+      <c r="F26" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="F26" s="22" t="s">
+      <c r="G26" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="H26" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I26" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J26" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J26" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L26" s="23" t="s">
+      <c r="M26" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N26" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O26" s="23" t="s">
-        <v>179</v>
-      </c>
       <c r="P26" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q26" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R26" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3513,57 +3705,57 @@
         <v>19</v>
       </c>
       <c r="C27" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="23" t="s">
+      <c r="F27" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="23" t="s">
+      <c r="H27" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="H27" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I27" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K27" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L27" s="23" t="s">
+      <c r="M27" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N27" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="M27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N27" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O27" s="23" t="s">
-        <v>184</v>
-      </c>
       <c r="P27" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R27" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -3587,52 +3779,52 @@
         <v>20</v>
       </c>
       <c r="C29" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="D29" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="23" t="s">
+      <c r="H29" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K29" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L29" s="23" t="s">
+      <c r="M29" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N29" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="M29" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N29" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O29" s="23" t="s">
-        <v>190</v>
-      </c>
       <c r="P29" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q29" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R29" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3640,52 +3832,52 @@
         <v>21</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="D30" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="23" t="s">
+      <c r="F30" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G30" s="23" t="s">
+      <c r="H30" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="H30" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I30" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K30" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L30" s="23" t="s">
+      <c r="M30" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N30" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="M30" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N30" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O30" s="23" t="s">
-        <v>195</v>
-      </c>
       <c r="P30" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q30" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R30" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3693,52 +3885,52 @@
         <v>22</v>
       </c>
       <c r="C31" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="D31" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="G31" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="H31" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K31" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="M31" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N31" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J31" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K31" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="M31" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N31" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O31" s="23" t="s">
-        <v>200</v>
-      </c>
       <c r="P31" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q31" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R31" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3746,57 +3938,57 @@
         <v>23</v>
       </c>
       <c r="C32" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="D32" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="23" t="s">
+      <c r="F32" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G32" s="23" t="s">
+      <c r="H32" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J32" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K32" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="H32" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J32" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K32" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L32" s="23" t="s">
+      <c r="M32" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N32" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="M32" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N32" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O32" s="23" t="s">
-        <v>205</v>
-      </c>
       <c r="P32" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q32" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R32" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -3820,52 +4012,52 @@
         <v>24</v>
       </c>
       <c r="C34" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="D34" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="23" t="s">
+      <c r="F34" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="F34" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="23" t="s">
+      <c r="H34" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K34" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="H34" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J34" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K34" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L34" s="23" t="s">
+      <c r="M34" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N34" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="M34" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N34" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O34" s="23" t="s">
-        <v>211</v>
-      </c>
       <c r="P34" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q34" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R34" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3873,52 +4065,52 @@
         <v>25</v>
       </c>
       <c r="C35" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="D35" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="23" t="s">
+      <c r="F35" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="23" t="s">
+      <c r="H35" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K35" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="M35" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N35" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="H35" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I35" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="J35" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K35" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L35" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="M35" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N35" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O35" s="23" t="s">
-        <v>216</v>
-      </c>
       <c r="P35" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q35" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R35" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -3926,2086 +4118,2086 @@
         <v>26</v>
       </c>
       <c r="C36" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="D36" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="23" t="s">
+      <c r="H36" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J36" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K36" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="M36" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N36" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="P36" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q36" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37" s="22">
+        <v>27</v>
+      </c>
+      <c r="C37" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="G36" s="23" t="s">
+      <c r="D37" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="H36" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J36" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K36" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L36" s="23" t="s">
+      <c r="F37" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="M36" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N36" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O36" s="23" t="s">
+      <c r="H37" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="P36" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q36" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R36" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="21" t="s">
+      <c r="M37" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N37" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="M37" s="21"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21"/>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
+      <c r="P37" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q37" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="38" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B38" s="22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C38" s="22" t="s">
         <v>224</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E38" s="23" t="s">
         <v>225</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>219</v>
+        <v>113</v>
       </c>
       <c r="G38" s="23" t="s">
         <v>226</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K38" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L38" s="23" t="s">
         <v>227</v>
       </c>
       <c r="M38" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N38" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O38" s="23" t="s">
         <v>228</v>
       </c>
       <c r="P38" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R38" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>229</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E39" s="23" t="s">
         <v>230</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="G39" s="23" t="s">
         <v>231</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I39" s="24" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="I39" s="26" t="s">
+        <v>91</v>
       </c>
       <c r="J39" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="27" t="s">
-        <v>28</v>
+        <v>76</v>
+      </c>
+      <c r="K39" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="L39" s="23" t="s">
         <v>232</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N39" s="27" t="s">
-        <v>28</v>
+        <v>76</v>
+      </c>
+      <c r="N39" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="O39" s="23" t="s">
         <v>233</v>
       </c>
       <c r="P39" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q39" s="27" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="Q39" s="25" t="s">
+        <v>21</v>
       </c>
       <c r="R39" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B40" s="22">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C40" s="22" t="s">
         <v>234</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E40" s="23" t="s">
         <v>235</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G40" s="23" t="s">
         <v>236</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K40" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L40" s="23" t="s">
         <v>237</v>
       </c>
       <c r="M40" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O40" s="23" t="s">
         <v>238</v>
       </c>
       <c r="P40" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q40" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R40" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B41" s="21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B41" s="22">
+        <v>31</v>
+      </c>
+      <c r="C41" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="21"/>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21"/>
-      <c r="P41" s="21"/>
-      <c r="Q41" s="21"/>
-      <c r="R41" s="21"/>
+      <c r="D41" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="H41" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J41" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K41" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="M41" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N41" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="P41" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q41" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="42" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="22">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>102</v>
+        <v>246</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K42" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="M42" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O42" s="23" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="P42" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q42" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R42" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="22">
+        <v>33</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>36</v>
-      </c>
       <c r="E43" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="F43" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="F43" s="22" t="s">
-        <v>133</v>
-      </c>
       <c r="G43" s="23" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J43" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K43" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M43" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N43" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O43" s="23" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="P43" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q43" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R43" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B44" s="22">
-        <v>32</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G44" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="H44" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I44" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J44" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="K44" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="L44" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="M44" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="N44" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="O44" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B44" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="P44" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q44" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="R44" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="45" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B45" s="21" t="s">
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21"/>
+      <c r="P44" s="21"/>
+      <c r="Q44" s="21"/>
+      <c r="R44" s="21"/>
+    </row>
+    <row r="45" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B45" s="22">
+        <v>34</v>
+      </c>
+      <c r="C45" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="21"/>
-      <c r="O45" s="21"/>
-      <c r="P45" s="21"/>
-      <c r="Q45" s="21"/>
-      <c r="R45" s="21"/>
+      <c r="D45" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H45" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J45" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="M45" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N45" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="P45" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q45" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="46" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="22">
+        <v>35</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="D46" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C46" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>39</v>
-      </c>
       <c r="E46" s="23" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K46" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="M46" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N46" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O46" s="23" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="P46" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q46" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R46" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M47" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N47" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O47" s="23" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="P47" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q47" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R47" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="22">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K48" s="25" t="s">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M48" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N48" s="25" t="s">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="N48" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="O48" s="23" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="P48" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q48" s="25" t="s">
-        <v>22</v>
+        <v>79</v>
+      </c>
+      <c r="Q48" s="27" t="s">
+        <v>27</v>
       </c>
       <c r="R48" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" s="22">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>133</v>
+        <v>175</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I49" s="26" t="s">
-        <v>92</v>
+        <v>74</v>
+      </c>
+      <c r="I49" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="J49" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K49" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N49" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O49" s="23" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="P49" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q49" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R49" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B50" s="22">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I50" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J50" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K50" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N50" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O50" s="23" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="P50" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q50" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R50" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B51" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
-      <c r="N51" s="21"/>
-      <c r="O51" s="21"/>
-      <c r="P51" s="21"/>
-      <c r="Q51" s="21"/>
-      <c r="R51" s="21"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B51" s="22">
+        <v>40</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I51" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J51" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N51" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="P51" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q51" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="52" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B52" s="22">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N52" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O52" s="23" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="P52" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q52" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R52" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B53" s="22">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>114</v>
+        <v>246</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K53" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L53" s="23" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="M53" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N53" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O53" s="23" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="P53" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q53" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R53" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="54" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B54" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="21"/>
-      <c r="M54" s="21"/>
-      <c r="N54" s="21"/>
-      <c r="O54" s="21"/>
-      <c r="P54" s="21"/>
-      <c r="Q54" s="21"/>
-      <c r="R54" s="21"/>
-    </row>
-    <row r="55" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B55" s="22">
-        <v>40</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="D55" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B54" s="22">
         <v>43</v>
       </c>
-      <c r="E55" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G55" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="H55" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I55" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J55" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K55" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L55" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="M55" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N55" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O55" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="P55" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q55" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R55" s="23" t="s">
-        <v>81</v>
-      </c>
+      <c r="C54" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J54" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K54" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="M54" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N54" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="P54" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q54" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B55" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
     </row>
     <row r="56" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B56" s="22">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N56" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O56" s="23" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="P56" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q56" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R56" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B57" s="22">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K57" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N57" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O57" s="23" t="s">
-        <v>124</v>
+        <v>316</v>
       </c>
       <c r="P57" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q57" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R57" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B58" s="22">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K58" s="25" t="s">
-        <v>22</v>
+        <v>75</v>
+      </c>
+      <c r="J58" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="K58" s="27" t="s">
+        <v>320</v>
       </c>
       <c r="L58" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="M58" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N58" s="25" t="s">
-        <v>22</v>
+        <v>321</v>
+      </c>
+      <c r="M58" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="N58" s="27" t="s">
+        <v>320</v>
       </c>
       <c r="O58" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="P58" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q58" s="25" t="s">
-        <v>22</v>
+        <v>322</v>
+      </c>
+      <c r="P58" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q58" s="27" t="s">
+        <v>320</v>
       </c>
       <c r="R58" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B59" s="22">
-        <v>44</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="F59" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="G59" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="H59" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J59" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K59" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L59" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="M59" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N59" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O59" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="P59" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q59" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R59" s="23" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B59" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
+      <c r="O59" s="21"/>
+      <c r="P59" s="21"/>
+      <c r="Q59" s="21"/>
+      <c r="R59" s="21"/>
     </row>
     <row r="60" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B60" s="22">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I60" s="26" t="s">
-        <v>92</v>
+        <v>74</v>
+      </c>
+      <c r="I60" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K60" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="M60" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N60" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O60" s="23" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="P60" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q60" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R60" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B61" s="22">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L61" s="23" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M61" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N61" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O61" s="23" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="P61" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q61" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R61" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B62" s="22">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M62" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N62" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O62" s="23" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="P62" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q62" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R62" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B63" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="21"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="21"/>
-      <c r="O63" s="21"/>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
-      <c r="R63" s="21"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B63" s="22">
+        <v>50</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I63" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J63" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="M63" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O63" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="P63" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R63" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="64" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B64" s="22">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K64" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="M64" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N64" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O64" s="23" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="P64" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q64" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R64" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B65" s="22">
-        <v>49</v>
-      </c>
-      <c r="C65" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K65" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L65" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="M65" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N65" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O65" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="P65" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R65" s="23" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B65" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+      <c r="F65" s="21"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21"/>
+      <c r="M65" s="21"/>
+      <c r="N65" s="21"/>
+      <c r="O65" s="21"/>
+      <c r="P65" s="21"/>
+      <c r="Q65" s="21"/>
+      <c r="R65" s="21"/>
     </row>
     <row r="66" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B66" s="22">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="F66" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J66" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K66" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L66" s="23" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M66" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N66" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O66" s="23" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="P66" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q66" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R66" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B67" s="22">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="H67" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J67" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K67" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="M67" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N67" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O67" s="23" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="P67" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q67" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R67" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B68" s="22">
-        <v>52</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="F68" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="G68" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="H68" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I68" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J68" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K68" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L68" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="M68" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N68" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O68" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="P68" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q68" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R68" s="23" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B68" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
     </row>
     <row r="69" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B69" s="22">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J69" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K69" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>210</v>
+        <v>364</v>
       </c>
       <c r="M69" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N69" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O69" s="23" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="P69" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q69" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R69" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B70" s="22">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I70" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K70" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L70" s="23" t="s">
-        <v>221</v>
+        <v>369</v>
       </c>
       <c r="M70" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N70" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O70" s="23" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="P70" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q70" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R70" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B71" s="22">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G71" s="23" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I71" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J71" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K71" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L71" s="23" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M71" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N71" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O71" s="23" t="s">
-        <v>369</v>
+        <v>123</v>
       </c>
       <c r="P71" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q71" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R71" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B72" s="22">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E72" s="23" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G72" s="23" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I72" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J72" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K72" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N72" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O72" s="23" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="P72" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q72" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R72" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B73" s="22">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K73" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="M73" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N73" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O73" s="23" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q73" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R73" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B74" s="22">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F74" s="22" t="s">
-        <v>176</v>
+        <v>113</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I74" s="24" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="I74" s="26" t="s">
+        <v>91</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K74" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="M74" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N74" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O74" s="23" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P74" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q74" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R74" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B75" s="22">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G75" s="23" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I75" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J75" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K75" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L75" s="23" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M75" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N75" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O75" s="23" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="P75" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q75" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R75" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B76" s="22">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="F76" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G76" s="23" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H76" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I76" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J76" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K76" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="M76" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N76" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O76" s="23" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="P76" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q76" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R76" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="77" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B77" s="22">
-        <v>61</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>394</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="F77" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="G77" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="H77" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="I77" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="J77" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="K77" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L77" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="M77" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N77" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O77" s="23" t="s">
-        <v>398</v>
-      </c>
-      <c r="P77" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q77" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R77" s="23" t="s">
-        <v>81</v>
-      </c>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B77" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="C77" s="21"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="21"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="21"/>
+      <c r="M77" s="21"/>
+      <c r="N77" s="21"/>
+      <c r="O77" s="21"/>
+      <c r="P77" s="21"/>
+      <c r="Q77" s="21"/>
+      <c r="R77" s="21"/>
     </row>
     <row r="78" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B78" s="22">
         <v>62</v>
       </c>
       <c r="C78" s="22" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F78" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G78" s="23" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H78" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I78" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J78" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K78" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L78" s="23" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M78" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N78" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O78" s="23" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P78" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q78" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R78" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
@@ -6013,444 +6205,1186 @@
         <v>63</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F79" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G79" s="23" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J79" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K79" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L79" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="K79" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L79" s="23" t="s">
-        <v>407</v>
-      </c>
       <c r="M79" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N79" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O79" s="23" t="s">
         <v>408</v>
       </c>
       <c r="P79" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q79" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R79" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B80" s="21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B80" s="22">
+        <v>64</v>
+      </c>
+      <c r="C80" s="22" t="s">
         <v>409</v>
       </c>
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
-      <c r="L80" s="21"/>
-      <c r="M80" s="21"/>
-      <c r="N80" s="21"/>
-      <c r="O80" s="21"/>
-      <c r="P80" s="21"/>
-      <c r="Q80" s="21"/>
-      <c r="R80" s="21"/>
+      <c r="D80" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="F80" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="H80" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I80" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J80" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K80" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L80" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="M80" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N80" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O80" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="P80" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q80" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R80" s="23" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="81" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B81" s="22">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F81" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="H81" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I81" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J81" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L81" s="23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M81" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N81" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O81" s="23" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="P81" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q81" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R81" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B82" s="22">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C82" s="22" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F82" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G82" s="23" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I82" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J82" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K82" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L82" s="23" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M82" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N82" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O82" s="23" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P82" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q82" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R82" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B83" s="22">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F83" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G83" s="23" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I83" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J83" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K83" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>424</v>
+        <v>242</v>
       </c>
       <c r="M83" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N83" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O83" s="23" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P83" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q83" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R83" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B84" s="22">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F84" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G84" s="23" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I84" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J84" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K84" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L84" s="23" t="s">
-        <v>429</v>
+        <v>209</v>
       </c>
       <c r="M84" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N84" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O84" s="23" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P84" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q84" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R84" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B85" s="22">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>431</v>
+        <v>271</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E85" s="23" t="s">
         <v>432</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G85" s="23" t="s">
         <v>433</v>
       </c>
       <c r="H85" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J85" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K85" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L85" s="23" t="s">
-        <v>221</v>
+        <v>434</v>
       </c>
       <c r="M85" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N85" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O85" s="23" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P85" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q85" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R85" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B86" s="22">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C86" s="22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F86" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G86" s="23" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H86" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L86" s="23" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M86" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N86" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O86" s="23" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P86" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q86" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R86" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B87" s="22">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F87" s="22" t="s">
-        <v>412</v>
+        <v>175</v>
       </c>
       <c r="G87" s="23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H87" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I87" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J87" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K87" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="M87" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N87" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="P87" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q87" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R87" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B88" s="22">
+        <v>72</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>447</v>
+      </c>
+      <c r="F88" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="H88" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I88" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J88" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K88" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="M88" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N88" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O88" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="P88" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q88" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R88" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B89" s="22">
+        <v>73</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="F89" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G89" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="H89" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I89" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J89" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K89" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L89" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="M89" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N89" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O89" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="P89" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q89" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R89" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B90" s="22">
+        <v>74</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="F90" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G90" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="H90" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I90" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J90" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K90" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L90" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="M90" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N90" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O90" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="P90" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q90" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R90" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B91" s="22">
+        <v>75</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="F91" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G91" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="H91" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I91" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J91" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K91" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L91" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="M91" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N91" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="P91" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q91" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R91" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B92" s="22">
+        <v>76</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="D92" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="F92" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G92" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="H92" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I92" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J92" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K92" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L92" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="M92" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N92" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O92" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="P92" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q92" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R92" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B93" s="22">
         <v>77</v>
       </c>
-      <c r="K87" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="L87" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="M87" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="N87" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="O87" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="P87" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q87" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="R87" s="23" t="s">
+      <c r="C93" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="D93" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="F93" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G93" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="H93" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I93" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J93" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K93" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L93" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="M93" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N93" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O93" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="P93" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q93" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R93" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B94" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="21"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+      <c r="L94" s="21"/>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21"/>
+      <c r="O94" s="21"/>
+      <c r="P94" s="21"/>
+      <c r="Q94" s="21"/>
+      <c r="R94" s="21"/>
+    </row>
+    <row r="95" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B95" s="22">
+        <v>78</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="D95" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="F95" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="H95" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I95" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J95" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K95" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L95" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="M95" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N95" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O95" s="23" t="s">
+        <v>481</v>
+      </c>
+      <c r="P95" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q95" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R95" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B96" s="22">
+        <v>79</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="D96" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="F96" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G96" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="H96" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I96" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J96" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K96" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L96" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="M96" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N96" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O96" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="P96" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q96" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R96" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B97" s="22">
+        <v>80</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="D97" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="F97" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G97" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="H97" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I97" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J97" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K97" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L97" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="M97" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N97" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O97" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="P97" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q97" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R97" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B98" s="22">
         <v>81</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="D98" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E98" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G98" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="H98" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I98" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J98" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K98" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L98" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="M98" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N98" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O98" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="P98" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q98" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R98" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B99" s="22">
+        <v>82</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E99" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G99" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="H99" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I99" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J99" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K99" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L99" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="M99" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N99" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O99" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="P99" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q99" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R99" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B100" s="22">
+        <v>83</v>
+      </c>
+      <c r="C100" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E100" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="F100" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G100" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="H100" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I100" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J100" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K100" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L100" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="M100" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N100" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O100" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="P100" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q100" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R100" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B101" s="22">
+        <v>84</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="D101" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E101" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="G101" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="I101" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="J101" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K101" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L101" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="M101" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="N101" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O101" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="P101" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q101" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R101" s="23" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -6462,13 +7396,13 @@
     <mergeCell ref="B20:R20"/>
     <mergeCell ref="B28:R28"/>
     <mergeCell ref="B33:R33"/>
-    <mergeCell ref="B37:R37"/>
-    <mergeCell ref="B41:R41"/>
-    <mergeCell ref="B45:R45"/>
-    <mergeCell ref="B51:R51"/>
-    <mergeCell ref="B54:R54"/>
-    <mergeCell ref="B63:R63"/>
-    <mergeCell ref="B80:R80"/>
+    <mergeCell ref="B44:R44"/>
+    <mergeCell ref="B55:R55"/>
+    <mergeCell ref="B59:R59"/>
+    <mergeCell ref="B65:R65"/>
+    <mergeCell ref="B68:R68"/>
+    <mergeCell ref="B77:R77"/>
+    <mergeCell ref="B94:R94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
